--- a/assets/constructions/examples/ctd_tsmb_bush2side.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_bush2side.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,11 +589,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MHCR20-4-5-4F</t>
+          <t>MHCR25-6-7-4F</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -607,16 +627,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -624,16 +644,16 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>18.8</v>
+        <v>23</v>
       </c>
       <c r="N2" t="n">
-        <v>18.8</v>
+        <v>23</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>83.5</v>
+        <v>110</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -645,12 +665,12 @@
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
-          <t>VAR_MICR:5</t>
+          <t>VAR_MICR:7</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>ISO_5609:20</t>
+          <t>ISO_5609:25</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -660,7 +680,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>VAR_MICR:4-5</t>
+          <t>VAR_MICR:6-7</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -681,11 +701,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>148.88</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>13687.09</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MHCR075-4-5-4F</t>
+          <t>MHCR22-4-5-4F</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -699,7 +733,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.05</v>
+        <v>22</v>
       </c>
       <c r="E3" t="n">
         <v>4</v>
@@ -708,7 +742,7 @@
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>19.05</v>
+        <v>22</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -716,16 +750,16 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>83.5</v>
+        <v>110</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -742,7 +776,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>ISO_5609:19.05</t>
+          <t>ISO_5609:22</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -773,11 +807,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>148.88</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>13687.09</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MHCR25-6-7-4F</t>
+          <t>MHCR20-4-5-4F</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -791,16 +839,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -808,16 +856,16 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>23</v>
+        <v>18.8</v>
       </c>
       <c r="N4" t="n">
-        <v>23</v>
+        <v>18.8</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>110</v>
+        <v>83.5</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -829,12 +877,12 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>VAR_MICR:7</t>
+          <t>VAR_MICR:5</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>ISO_5609:25</t>
+          <t>ISO_5609:20</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -844,7 +892,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>VAR_MICR:6-7</t>
+          <t>VAR_MICR:4-5</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -865,11 +913,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>148.88</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>13687.09</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MHCR20-6-7-4F</t>
+          <t>MHCR25-4-5-4F</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -883,16 +945,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -900,16 +962,16 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>18.8</v>
+        <v>23</v>
       </c>
       <c r="N5" t="n">
-        <v>18.8</v>
+        <v>23</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>83.5</v>
+        <v>110</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -921,12 +983,12 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>VAR_MICR:7</t>
+          <t>VAR_MICR:5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>ISO_5609:20</t>
+          <t>ISO_5609:25</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -936,7 +998,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>VAR_MICR:6-7</t>
+          <t>VAR_MICR:4-5</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -957,11 +1019,25 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>148.88</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>13687.09</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MHCR22-4-5-4F</t>
+          <t>MHCR075-4-5-4F</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -975,7 +1051,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>19.05</v>
       </c>
       <c r="E6" t="n">
         <v>4</v>
@@ -984,7 +1060,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>22</v>
+        <v>19.05</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -992,16 +1068,16 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="N6" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>110</v>
+        <v>83.5</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1018,7 +1094,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>ISO_5609:22</t>
+          <t>ISO_5609:19.05</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1048,6 +1124,20 @@
         <is>
           <t>2019 / Groovex Catalog</t>
         </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>148.88</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>13687.09</v>
       </c>
     </row>
   </sheetData>
